--- a/VerveStacks_AUS_grids_kan50/vt_vervestacks_AUS_v1.xlsx
+++ b/VerveStacks_AUS_grids_kan50/vt_vervestacks_AUS_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4DB5BFE-A3A5-4B79-AB9B-C57B8B48379D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CFDB5143-1B54-4E84-A0A9-378974491A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{8E4D9073-B133-4BD6-BBAA-06D6DDB5D83C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2217E7F5-EF56-4FFC-830C-F5016C9C852C}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -1838,12 +1838,12 @@
     <t>Aggregated Plant -- construction -- CHP</t>
   </si>
   <si>
+    <t>IRENA Gap - bioenergy (2024) - way/171744075-275_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - bioenergy (2022) - way/171744075-275_Missing Bioenergy Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - bioenergy (2024) - way/171744075-275_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
     <t>Bayswater power station_Unit 1 -- operating</t>
   </si>
   <si>
@@ -2303,48 +2303,48 @@
     <t>Aggregated Plant - EMBER Gap - way/229759860-220_Missing Gas Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - hydro (2022) - way/160201298-330_Missing Hydro Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - hydro (2024) - way/160201298-330_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - hydro (2022) - way/160201298-330_Missing Hydro Capacity -- operating</t>
+    <t>IRENA Gap - hydro (2022) - way/170832455-275_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - hydro (2024) - way/170832455-275_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - hydro (2022) - way/170832455-275_Missing Hydro Capacity -- operating</t>
+    <t>IRENA Gap - hydro (2022) - AU73-330_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - hydro (2024) - AU73-330_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - hydro (2022) - AU73-330_Missing Hydro Capacity -- operating</t>
-  </si>
-  <si>
     <t>IRENA Gap - hydro (2024) - way/171728751-275_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - hydro (2022) - way/171728751-275_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - hydro (2024) - way/169408193-330_Missing Hydro Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - hydro (2022) - way/169408193-330_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - hydro (2024) - way/169408193-330_Missing Hydro Capacity -- operating</t>
-  </si>
-  <si>
     <t>IRENA Gap - hydro (2022) - way/174875093-330_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - hydro (2024) - way/174875093-330_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - hydro (2022) - way/166113109-275_Missing Hydro Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - hydro (2024) - way/166113109-275_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - hydro (2022) - way/166113109-275_Missing Hydro Capacity -- operating</t>
-  </si>
-  <si>
     <t>IRENA Gap - hydro (2024) - way/174441055-220_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
@@ -2363,12 +2363,12 @@
     <t>IRENA Gap - hydro (2024) - way/925410265-330_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - hydro (2022) - way/208359871-330_Missing Hydro Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - hydro (2024) - way/208359871-330_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - hydro (2022) - way/208359871-330_Missing Hydro Capacity -- operating</t>
-  </si>
-  <si>
     <t>Bastyan hydroelectric plant_ -- operating</t>
   </si>
   <si>
@@ -2528,30 +2528,30 @@
     <t>HEZ Energy Peaking Power Plant_1-1 -- operating -- CHP (captive)</t>
   </si>
   <si>
+    <t>IRENA Gap - solar (2024) - 15_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
+    <t>IRENA Gap - solar (2022) - 15_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - solar (2023) - 15_Missing Solar Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - solar (2022) - 15_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
-    <t>IRENA Gap - solar (2024) - 15_Missing Solar Capacity -- operating</t>
+    <t>IRENA Gap - solar (2024) - 20_Missing Solar Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - solar (2023) - 20_Missing Solar Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - solar (2024) - 20_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
     <t>IRENA Gap - solar (2022) - 20_Missing Solar Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - solar (2023) - 30_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - solar (2024) - 30_Missing Solar Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - solar (2023) - 30_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
     <t>IRENA Gap - solar (2022) - 30_Missing Solar Capacity -- operating</t>
   </si>
   <si>
@@ -2621,22 +2621,22 @@
     <t>Goorambat East solar farm_-- -- construction</t>
   </si>
   <si>
+    <t>IRENA Gap - windon (2023) - 77_Missing Onshore wind energy Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - windon (2022) - 77_Missing Onshore wind energy Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - windon (2023) - 77_Missing Onshore wind energy Capacity -- operating</t>
+    <t>IRENA Gap - windon (2023) - 83_Missing Onshore wind energy Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - windon (2022) - 83_Missing Onshore wind energy Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - windon (2023) - 83_Missing Onshore wind energy Capacity -- operating</t>
+    <t>IRENA Gap - windon (2022) - 95_Missing Onshore wind energy Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - windon (2023) - 95_Missing Onshore wind energy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>IRENA Gap - windon (2022) - 95_Missing Onshore wind energy Capacity -- operating</t>
   </si>
   <si>
     <t>MacIntyre precinct wind farm_MacIntyre -- operating</t>
@@ -6655,7 +6655,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B848B422-BDA0-433A-B58C-2E74C38AC51E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{013896DA-E00F-4463-8E2C-B01D2494AA76}">
   <dimension ref="B9:V220"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19347,7 +19347,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F5AED54-B640-4594-AE86-5CA6A85A8381}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{213EB6B1-CC6B-42C5-B6B7-D448A96EA039}">
   <dimension ref="B9:Y454"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -46052,7 +46052,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3DD3221-D345-4B2F-A11B-9E44B1AFE19F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DADD5B9C-AD8B-4423-85BB-49F2392A7C29}">
   <dimension ref="B9:Y655"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -46309,7 +46309,7 @@
         <v>17</v>
       </c>
       <c r="U13" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="V13" t="s">
         <v>585</v>
@@ -46321,7 +46321,7 @@
         <v>587</v>
       </c>
       <c r="Y13" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
     </row>
     <row r="14" spans="2:25" x14ac:dyDescent="0.45">
@@ -46368,7 +46368,7 @@
         <v>17</v>
       </c>
       <c r="U14" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="V14" t="s">
         <v>585</v>
@@ -46380,7 +46380,7 @@
         <v>587</v>
       </c>
       <c r="Y14" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="15" spans="2:25" x14ac:dyDescent="0.45">
@@ -65340,7 +65340,7 @@
         <v>17</v>
       </c>
       <c r="U341" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="V341" t="s">
         <v>585</v>
@@ -65402,7 +65402,7 @@
         <v>17</v>
       </c>
       <c r="U342" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="V342" t="s">
         <v>585</v>
@@ -65588,7 +65588,7 @@
         <v>17</v>
       </c>
       <c r="U345" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="V345" t="s">
         <v>585</v>
@@ -65650,7 +65650,7 @@
         <v>17</v>
       </c>
       <c r="U346" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="V346" t="s">
         <v>585</v>
@@ -65712,7 +65712,7 @@
         <v>17</v>
       </c>
       <c r="U347" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="V347" t="s">
         <v>585</v>
@@ -65774,7 +65774,7 @@
         <v>17</v>
       </c>
       <c r="U348" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="V348" t="s">
         <v>585</v>
@@ -65898,7 +65898,7 @@
         <v>17</v>
       </c>
       <c r="U350" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="V350" t="s">
         <v>585</v>
@@ -65960,7 +65960,7 @@
         <v>17</v>
       </c>
       <c r="U351" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="V351" t="s">
         <v>585</v>
@@ -79927,7 +79927,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE39E2C2-30E8-48FA-93CA-B51C4C2BE88C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4B23FBE-824B-4491-B76F-58E5B83164FA}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_AUS_grids_kan50/vt_vervestacks_AUS_v1.xlsx
+++ b/VerveStacks_AUS_grids_kan50/vt_vervestacks_AUS_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{77A16995-F396-4085-9316-CD72E56A9F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{99ABF87F-55D2-491E-9E3F-4759A156DBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2015CE13-B220-40AA-9812-8566862507C2}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A9F31588-38AB-4455-A7F1-ED75190A3C1E}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -1841,12 +1841,12 @@
     <t>Aggregated Plant -- construction -- CHP</t>
   </si>
   <si>
+    <t>IRENA Gap - bioenergy (2022) - way/171744075-275_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - bioenergy (2024) - way/171744075-275_Missing Bioenergy Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - bioenergy (2022) - way/171744075-275_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
     <t>Bayswater power station_Unit 1 -- operating</t>
   </si>
   <si>
@@ -2306,30 +2306,30 @@
     <t>Solomon Hub mine power station_1-1 -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - hydro (2024) - way/160201298-330_Missing Hydro Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - hydro (2022) - way/160201298-330_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - hydro (2024) - way/160201298-330_Missing Hydro Capacity -- operating</t>
-  </si>
-  <si>
     <t>IRENA Gap - hydro (2024) - way/172587651-275_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - hydro (2022) - way/172587651-275_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - hydro (2024) - AU73-330_Missing Hydro Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - hydro (2022) - AU73-330_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - hydro (2024) - AU73-330_Missing Hydro Capacity -- operating</t>
+    <t>IRENA Gap - hydro (2024) - way/171728751-275_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - hydro (2022) - way/171728751-275_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - hydro (2024) - way/171728751-275_Missing Hydro Capacity -- operating</t>
-  </si>
-  <si>
     <t>IRENA Gap - hydro (2024) - way/174875093-330_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
@@ -2360,12 +2360,12 @@
     <t>IRENA Gap - hydro (2022) - way/925410265-330_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - hydro (2024) - way/208359871-330_Missing Hydro Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - hydro (2022) - way/208359871-330_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - hydro (2024) - way/208359871-330_Missing Hydro Capacity -- operating</t>
-  </si>
-  <si>
     <t>Bastyan hydroelectric plant_ -- operating</t>
   </si>
   <si>
@@ -2525,22 +2525,25 @@
     <t>HEZ Energy Peaking Power Plant_1-1 -- operating -- CHP (captive)</t>
   </si>
   <si>
+    <t>IRENA Gap - solar (2024) - 11_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
+    <t>IRENA Gap - solar (2022) - 11_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - solar (2023) - 11_Missing Solar Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - solar (2022) - 11_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
-    <t>IRENA Gap - solar (2024) - 11_Missing Solar Capacity -- operating</t>
+    <t>IRENA Gap - solar (2024) - 20_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
+    <t>IRENA Gap - solar (2023) - 20_Missing Solar Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - solar (2022) - 20_Missing Solar Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - solar (2023) - 20_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
-    <t>IRENA Gap - solar (2024) - 20_Missing Solar Capacity -- operating</t>
+    <t>IRENA Gap - solar (2024) - 36_Missing Solar Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - solar (2023) - 36_Missing Solar Capacity -- operating</t>
@@ -2549,9 +2552,6 @@
     <t>IRENA Gap - solar (2022) - 36_Missing Solar Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - solar (2024) - 36_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
     <t>Aldoga solar farm_1 -- construction</t>
   </si>
   <si>
@@ -2624,10 +2624,10 @@
     <t>IRENA Gap - windon (2023) - 69_Missing Onshore wind energy Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - windon (2022) - 82_Missing Onshore wind energy Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - windon (2023) - 82_Missing Onshore wind energy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>IRENA Gap - windon (2022) - 82_Missing Onshore wind energy Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - windon (2022) - 83_Missing Onshore wind energy Capacity -- operating</t>
@@ -6664,7 +6664,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18D431B7-5DFB-47DE-B514-D0FB9A707EA7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CBD0BC7-221F-4B63-A5DC-497BD7A4C361}">
   <dimension ref="B9:V222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19504,7 +19504,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A016F14-9848-4F71-8353-BE8306518E58}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A3025AC-22E2-485E-B68E-2ED0F385A8EA}">
   <dimension ref="B9:Y454"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -46209,7 +46209,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{682BCE57-9EE6-41B4-87B2-38B307D97A0D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F553641-DDBE-4F7A-AA80-00B70C7E97CC}">
   <dimension ref="B9:Y655"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -65063,7 +65063,7 @@
         <v>17</v>
       </c>
       <c r="U334" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="V334" t="s">
         <v>586</v>
@@ -65125,7 +65125,7 @@
         <v>17</v>
       </c>
       <c r="U335" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="V335" t="s">
         <v>586</v>
@@ -65311,7 +65311,7 @@
         <v>17</v>
       </c>
       <c r="U338" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="V338" t="s">
         <v>586</v>
@@ -65373,7 +65373,7 @@
         <v>17</v>
       </c>
       <c r="U339" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="V339" t="s">
         <v>586</v>
@@ -65559,7 +65559,7 @@
         <v>17</v>
       </c>
       <c r="U342" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="V342" t="s">
         <v>586</v>
@@ -65621,7 +65621,7 @@
         <v>17</v>
       </c>
       <c r="U343" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="V343" t="s">
         <v>586</v>
@@ -65807,7 +65807,7 @@
         <v>17</v>
       </c>
       <c r="U346" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="V346" t="s">
         <v>586</v>
@@ -65869,7 +65869,7 @@
         <v>17</v>
       </c>
       <c r="U347" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="V347" t="s">
         <v>586</v>
@@ -66117,7 +66117,7 @@
         <v>17</v>
       </c>
       <c r="U351" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="V351" t="s">
         <v>586</v>
@@ -66179,7 +66179,7 @@
         <v>17</v>
       </c>
       <c r="U352" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="V352" t="s">
         <v>586</v>
@@ -67915,7 +67915,7 @@
         <v>17</v>
       </c>
       <c r="U380" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="V380" t="s">
         <v>586</v>
@@ -67977,7 +67977,7 @@
         <v>17</v>
       </c>
       <c r="U381" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="V381" t="s">
         <v>586</v>
@@ -76002,7 +76002,7 @@
         <v>33</v>
       </c>
       <c r="P546">
-        <v>0.28671921074143963</v>
+        <v>0.28671921074143969</v>
       </c>
     </row>
     <row r="547" spans="2:16" x14ac:dyDescent="0.45">
@@ -76031,7 +76031,7 @@
         <v>32</v>
       </c>
       <c r="P547">
-        <v>0.28671921074143963</v>
+        <v>0.28671921074143969</v>
       </c>
     </row>
     <row r="548" spans="2:16" x14ac:dyDescent="0.45">
@@ -76060,7 +76060,7 @@
         <v>33</v>
       </c>
       <c r="P548">
-        <v>0.28671921074143963</v>
+        <v>0.28671921074143969</v>
       </c>
     </row>
     <row r="549" spans="2:16" x14ac:dyDescent="0.45">
@@ -76089,7 +76089,7 @@
         <v>32</v>
       </c>
       <c r="P549">
-        <v>0.28671921074143963</v>
+        <v>0.28671921074143969</v>
       </c>
     </row>
     <row r="550" spans="2:16" x14ac:dyDescent="0.45">
@@ -76118,7 +76118,7 @@
         <v>33</v>
       </c>
       <c r="P550">
-        <v>0.28671921074143963</v>
+        <v>0.28671921074143969</v>
       </c>
     </row>
     <row r="551" spans="2:16" x14ac:dyDescent="0.45">
@@ -76147,7 +76147,7 @@
         <v>32</v>
       </c>
       <c r="P551">
-        <v>0.28671921074143963</v>
+        <v>0.28671921074143969</v>
       </c>
     </row>
     <row r="552" spans="2:16" x14ac:dyDescent="0.45">
@@ -80108,7 +80108,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F18BE8DA-167F-42BD-B51C-95B9C8B6F8B2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3080B22E-F5FC-4BDC-A7D5-E7A05CFC4AC9}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_AUS_grids_kan50/vt_vervestacks_AUS_v1.xlsx
+++ b/VerveStacks_AUS_grids_kan50/vt_vervestacks_AUS_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F2DE3BC-13DB-4747-9DC0-419FE39E3F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB4228B7-AD9B-481D-8A1C-7DA7CB163836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{7ED3CCC0-182A-4431-8FF4-663332B5405B}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{27A1B61E-869A-4851-925B-1386F706E1F4}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -1841,12 +1841,12 @@
     <t>Aggregated Plant -- construction -- CHP</t>
   </si>
   <si>
+    <t>IRENA Gap - bioenergy (2024) - way/171744075-275_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - bioenergy (2022) - way/171744075-275_Missing Bioenergy Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - bioenergy (2024) - way/171744075-275_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
     <t>Bayswater power station_Unit 1 -- operating</t>
   </si>
   <si>
@@ -2312,12 +2312,12 @@
     <t>IRENA Gap - hydro (2024) - way/160201298-330_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - hydro (2022) - way/172587651-275_Missing Hydro Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - hydro (2024) - way/172587651-275_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - hydro (2022) - way/172587651-275_Missing Hydro Capacity -- operating</t>
-  </si>
-  <si>
     <t>IRENA Gap - hydro (2022) - AU73-330_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
@@ -2348,12 +2348,12 @@
     <t>IRENA Gap - hydro (2024) - way/166113109-275_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - hydro (2024) - way/174441055-220_Missing Hydro Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - hydro (2022) - way/174441055-220_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - hydro (2024) - way/174441055-220_Missing Hydro Capacity -- operating</t>
-  </si>
-  <si>
     <t>IRENA Gap - hydro (2022) - way/88191017-220_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
@@ -2531,33 +2531,33 @@
     <t>HEZ Energy Peaking Power Plant_1-1 -- operating -- CHP (captive)</t>
   </si>
   <si>
+    <t>IRENA Gap - solar (2023) - 11_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - solar (2022) - 11_Missing Solar Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - solar (2023) - 11_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
     <t>IRENA Gap - solar (2024) - 11_Missing Solar Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - solar (2023) - 20_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - solar (2024) - 20_Missing Solar Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - solar (2023) - 20_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
     <t>IRENA Gap - solar (2022) - 20_Missing Solar Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - solar (2023) - 36_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - solar (2024) - 36_Missing Solar Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - solar (2022) - 36_Missing Solar Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - solar (2023) - 36_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
     <t>Aldoga solar farm_1 -- construction</t>
   </si>
   <si>
@@ -2630,10 +2630,10 @@
     <t>IRENA Gap - windon (2023) - 69_Missing Onshore wind energy Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - windon (2023) - 82_Missing Onshore wind energy Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - windon (2022) - 82_Missing Onshore wind energy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>IRENA Gap - windon (2023) - 82_Missing Onshore wind energy Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - windon (2023) - 83_Missing Onshore wind energy Capacity -- operating</t>
@@ -6667,7 +6667,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18757C84-6CC6-479B-90F1-F44C23FC540F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81291E9B-E571-4921-A97F-9DB5264FF238}">
   <dimension ref="B9:Y222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6770,10 +6770,10 @@
         <v>3583</v>
       </c>
       <c r="H11">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="I11">
-        <v>10.09</v>
+        <v>10.59</v>
       </c>
       <c r="J11">
         <v>1.2</v>
@@ -6838,10 +6838,10 @@
         <v>3583</v>
       </c>
       <c r="H12">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="I12">
-        <v>10.59</v>
+        <v>10.09</v>
       </c>
       <c r="J12">
         <v>1.2</v>
@@ -17152,10 +17152,10 @@
         <v>1365</v>
       </c>
       <c r="H177">
-        <v>56.2</v>
+        <v>60.2</v>
       </c>
       <c r="I177">
-        <v>8.15</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="M177">
         <v>0.84455000000000002</v>
@@ -17338,10 +17338,10 @@
         <v>1365</v>
       </c>
       <c r="H180">
-        <v>60.2</v>
+        <v>56.2</v>
       </c>
       <c r="I180">
-        <v>8.5500000000000007</v>
+        <v>8.15</v>
       </c>
       <c r="M180">
         <v>0.84455000000000002</v>
@@ -17586,10 +17586,10 @@
         <v>1365</v>
       </c>
       <c r="H184">
-        <v>60.2</v>
+        <v>56.2</v>
       </c>
       <c r="I184">
-        <v>8.5499999999999989</v>
+        <v>8.15</v>
       </c>
       <c r="M184">
         <v>0.84455000000000002</v>
@@ -17651,7 +17651,7 @@
         <v>60.2</v>
       </c>
       <c r="I185">
-        <v>8.5500000000000007</v>
+        <v>8.5499999999999989</v>
       </c>
       <c r="M185">
         <v>0.84455000000000002</v>
@@ -17710,10 +17710,10 @@
         <v>1365</v>
       </c>
       <c r="H186">
-        <v>56.2</v>
+        <v>60.2</v>
       </c>
       <c r="I186">
-        <v>8.15</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="M186">
         <v>0.84455000000000002</v>
@@ -17958,10 +17958,10 @@
         <v>1365</v>
       </c>
       <c r="H190">
-        <v>60.2</v>
+        <v>56.2</v>
       </c>
       <c r="I190">
-        <v>8.5500000000000007</v>
+        <v>8.15</v>
       </c>
       <c r="M190">
         <v>0.84455000000000002</v>
@@ -18020,10 +18020,10 @@
         <v>1365</v>
       </c>
       <c r="H191">
-        <v>56.2</v>
+        <v>60.2</v>
       </c>
       <c r="I191">
-        <v>8.15</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="M191">
         <v>0.84455000000000002</v>
@@ -19618,7 +19618,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5C05F2D-F8B3-48DB-BDDE-64FA8B82947B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7664298F-98D9-48F6-BE9F-2011C612B187}">
   <dimension ref="B9:Y454"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -46323,7 +46323,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8C7954B-4B40-4101-9378-A4FB5AE3EFC6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F973E70-658A-4E59-9940-2465778A3E69}">
   <dimension ref="B9:Y657"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -55519,19 +55519,19 @@
         <v>2014</v>
       </c>
       <c r="G167">
-        <v>8.5999999999999993E-2</v>
+        <v>0.06</v>
       </c>
       <c r="H167">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="I167">
-        <v>1080</v>
+        <v>919.99999999999989</v>
       </c>
       <c r="J167">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="K167">
-        <v>4.8</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="O167">
         <v>41</v>
@@ -55578,19 +55578,19 @@
         <v>2014</v>
       </c>
       <c r="G168">
-        <v>0.06</v>
+        <v>8.5999999999999993E-2</v>
       </c>
       <c r="H168">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="I168">
-        <v>919.99999999999989</v>
+        <v>1080</v>
       </c>
       <c r="J168">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K168">
-        <v>4.4000000000000004</v>
+        <v>4.8</v>
       </c>
       <c r="O168">
         <v>41</v>
@@ -64717,7 +64717,7 @@
         <v>33</v>
       </c>
       <c r="P326">
-        <v>0.19048331226722054</v>
+        <v>0.19048331226722051</v>
       </c>
       <c r="R326" t="s">
         <v>590</v>
@@ -64770,7 +64770,7 @@
         <v>32</v>
       </c>
       <c r="P327">
-        <v>0.19048331226722054</v>
+        <v>0.19048331226722051</v>
       </c>
       <c r="R327" t="s">
         <v>590</v>
@@ -64823,7 +64823,7 @@
         <v>31</v>
       </c>
       <c r="P328">
-        <v>0.19048331226722054</v>
+        <v>0.19048331226722051</v>
       </c>
       <c r="R328" t="s">
         <v>590</v>
@@ -64876,7 +64876,7 @@
         <v>33</v>
       </c>
       <c r="P329">
-        <v>0.19048331226722054</v>
+        <v>0.19048331226722051</v>
       </c>
       <c r="R329" t="s">
         <v>590</v>
@@ -64929,7 +64929,7 @@
         <v>32</v>
       </c>
       <c r="P330">
-        <v>0.19048331226722054</v>
+        <v>0.19048331226722051</v>
       </c>
       <c r="R330" t="s">
         <v>590</v>
@@ -64982,7 +64982,7 @@
         <v>31</v>
       </c>
       <c r="P331">
-        <v>0.19048331226722054</v>
+        <v>0.19048331226722051</v>
       </c>
       <c r="R331" t="s">
         <v>590</v>
@@ -65035,7 +65035,7 @@
         <v>33</v>
       </c>
       <c r="P332">
-        <v>0.19048331226722054</v>
+        <v>0.19048331226722051</v>
       </c>
       <c r="R332" t="s">
         <v>590</v>
@@ -65088,7 +65088,7 @@
         <v>32</v>
       </c>
       <c r="P333">
-        <v>0.19048331226722054</v>
+        <v>0.19048331226722051</v>
       </c>
       <c r="R333" t="s">
         <v>590</v>
@@ -65141,7 +65141,7 @@
         <v>31</v>
       </c>
       <c r="P334">
-        <v>0.19048331226722054</v>
+        <v>0.19048331226722051</v>
       </c>
       <c r="R334" t="s">
         <v>590</v>
@@ -65277,7 +65277,7 @@
         <v>17</v>
       </c>
       <c r="U336" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="V336" t="s">
         <v>586</v>
@@ -65339,7 +65339,7 @@
         <v>17</v>
       </c>
       <c r="U337" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="V337" t="s">
         <v>586</v>
@@ -65773,7 +65773,7 @@
         <v>17</v>
       </c>
       <c r="U344" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="V344" t="s">
         <v>586</v>
@@ -65835,7 +65835,7 @@
         <v>17</v>
       </c>
       <c r="U345" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="V345" t="s">
         <v>586</v>
@@ -68129,7 +68129,7 @@
         <v>17</v>
       </c>
       <c r="U382" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="V382" t="s">
         <v>586</v>
@@ -68191,7 +68191,7 @@
         <v>17</v>
       </c>
       <c r="U383" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="V383" t="s">
         <v>586</v>
@@ -80322,7 +80322,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37C158C6-9836-4D76-97D1-4861346FF755}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF897571-0E93-4752-A9FE-97D5F5E724CC}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_AUS_grids_kan50/vt_vervestacks_AUS_v1.xlsx
+++ b/VerveStacks_AUS_grids_kan50/vt_vervestacks_AUS_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E983C1E-2657-4720-8B35-B640870F297B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7437967-F8FB-4891-8633-EFFA3A9F19AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5AD74F12-6B35-4894-81B3-7E24E048CBC9}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{13E2DA83-996D-4DE4-AD24-8FE585ED2296}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -887,18 +887,12 @@
     <t>ep_gas_steam_turbine_G100000413432</t>
   </si>
   <si>
-    <t>ep_hydro_AUS42p8S146p2E_AUS__irena</t>
+    <t>ep_hydro_Armidale_AUS__irena</t>
   </si>
   <si>
     <t>hydro</t>
   </si>
   <si>
-    <t>e_AUS42p8S146p2E_AUS</t>
-  </si>
-  <si>
-    <t>ep_hydro_Armidale_AUS__irena</t>
-  </si>
-  <si>
     <t>e_Armidale_AUS</t>
   </si>
   <si>
@@ -911,6 +905,12 @@
     <t>ep_hydro_GinGin_AUS__irena</t>
   </si>
   <si>
+    <t>ep_hydro_Hobart_AUS__irena</t>
+  </si>
+  <si>
+    <t>e_Hobart_AUS</t>
+  </si>
+  <si>
     <t>ep_hydro_MountPiper_AUS__irena</t>
   </si>
   <si>
@@ -2345,34 +2345,34 @@
     <t>Solomon Hub mine power station_1-1 -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - hydro (2022) - AU149-220_Missing Hydro Capacity -- operating</t>
-  </si>
-  <si>
-    <t>IRENA Gap - hydro (2024) - AU149-220_Missing Hydro Capacity -- operating</t>
-  </si>
-  <si>
     <t>IRENA Gap - hydro (2022) - way/160201298-330_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - hydro (2024) - way/160201298-330_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - hydro (2022) - way/172587651-275_Missing Hydro Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - hydro (2024) - way/172587651-275_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - hydro (2022) - way/172587651-275_Missing Hydro Capacity -- operating</t>
-  </si>
-  <si>
     <t>IRENA Gap - hydro (2022) - AU73-330_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - hydro (2024) - AU73-330_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - hydro (2022) - way/171728751-275_Missing Hydro Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - hydro (2024) - way/171728751-275_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - hydro (2022) - way/171728751-275_Missing Hydro Capacity -- operating</t>
+    <t>IRENA Gap - hydro (2024) - AU146-220_Missing Hydro Capacity -- operating</t>
+  </si>
+  <si>
+    <t>IRENA Gap - hydro (2022) - AU146-220_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - hydro (2024) - way/169408193-330_Missing Hydro Capacity -- operating</t>
@@ -2381,36 +2381,36 @@
     <t>IRENA Gap - hydro (2022) - way/169408193-330_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - hydro (2022) - way/174875093-330_Missing Hydro Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - hydro (2024) - way/174875093-330_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - hydro (2022) - way/174875093-330_Missing Hydro Capacity -- operating</t>
+    <t>IRENA Gap - hydro (2024) - way/166113109-275_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - hydro (2022) - way/166113109-275_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - hydro (2024) - way/166113109-275_Missing Hydro Capacity -- operating</t>
+    <t>IRENA Gap - hydro (2022) - way/88191017-220_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - hydro (2024) - way/88191017-220_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - hydro (2022) - way/88191017-220_Missing Hydro Capacity -- operating</t>
-  </si>
-  <si>
     <t>IRENA Gap - hydro (2024) - way/925410265-330_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - hydro (2022) - way/925410265-330_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - hydro (2024) - way/208359871-330_Missing Hydro Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - hydro (2022) - way/208359871-330_Missing Hydro Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - hydro (2024) - way/208359871-330_Missing Hydro Capacity -- operating</t>
-  </si>
-  <si>
     <t>Bastyan hydroelectric plant_ -- operating</t>
   </si>
   <si>
@@ -2573,21 +2573,21 @@
     <t>IRENA Gap - solar (2022) - 40_Missing Solar Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - solar (2024) - 40_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - solar (2023) - 40_Missing Solar Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - solar (2024) - 40_Missing Solar Capacity -- operating</t>
+    <t>IRENA Gap - solar (2023) - 48_Missing Solar Capacity -- operating</t>
+  </si>
+  <si>
+    <t>IRENA Gap - solar (2022) - 48_Missing Solar Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - solar (2024) - 48_Missing Solar Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - solar (2023) - 48_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
-    <t>IRENA Gap - solar (2022) - 48_Missing Solar Capacity -- operating</t>
-  </si>
-  <si>
     <t>IRENA Gap - solar (2023) - 49_Missing Solar Capacity -- operating</t>
   </si>
   <si>
@@ -2663,24 +2663,24 @@
     <t>Goorambat East solar farm_-- -- construction</t>
   </si>
   <si>
+    <t>IRENA Gap - windon (2023) - 45_Missing Onshore wind energy Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - windon (2022) - 45_Missing Onshore wind energy Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - windon (2023) - 45_Missing Onshore wind energy Capacity -- operating</t>
-  </si>
-  <si>
     <t>IRENA Gap - windon (2023) - 70_Missing Onshore wind energy Capacity -- operating</t>
   </si>
   <si>
     <t>IRENA Gap - windon (2022) - 70_Missing Onshore wind energy Capacity -- operating</t>
   </si>
   <si>
+    <t>IRENA Gap - windon (2023) - 71_Missing Onshore wind energy Capacity -- operating</t>
+  </si>
+  <si>
     <t>IRENA Gap - windon (2022) - 71_Missing Onshore wind energy Capacity -- operating</t>
   </si>
   <si>
-    <t>IRENA Gap - windon (2023) - 71_Missing Onshore wind energy Capacity -- operating</t>
-  </si>
-  <si>
     <t>MacIntyre precinct wind farm_MacIntyre -- operating</t>
   </si>
   <si>
@@ -3050,7 +3050,7 @@
     <t>en_a_windoff_wind_G100000927844</t>
   </si>
   <si>
-    <t>elc_wof_AUS_003</t>
+    <t>elc_wof_AUS_004</t>
   </si>
   <si>
     <t>en_a_windoff_wind_G100000927854</t>
@@ -6754,7 +6754,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26C72211-399A-4DCB-A61D-B92B06DD0134}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D599735E-2816-4F88-9AA9-E55DB22E4486}">
   <dimension ref="B9:Y222"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14443,10 +14443,10 @@
         <v>1365</v>
       </c>
       <c r="H132">
-        <v>56.2</v>
+        <v>60.2</v>
       </c>
       <c r="I132">
-        <v>8.15</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="M132">
         <v>0.84455000000000002</v>
@@ -14505,10 +14505,10 @@
         <v>1365</v>
       </c>
       <c r="H133">
-        <v>56.2</v>
+        <v>60.2</v>
       </c>
       <c r="I133">
-        <v>8.15</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="M133">
         <v>0.84455000000000002</v>
@@ -14567,10 +14567,10 @@
         <v>1365</v>
       </c>
       <c r="H134">
-        <v>60.2</v>
+        <v>56.2</v>
       </c>
       <c r="I134">
-        <v>8.5500000000000007</v>
+        <v>8.15</v>
       </c>
       <c r="M134">
         <v>0.84455000000000002</v>
@@ -14629,10 +14629,10 @@
         <v>1365</v>
       </c>
       <c r="H135">
-        <v>60.2</v>
+        <v>56.2</v>
       </c>
       <c r="I135">
-        <v>8.5500000000000007</v>
+        <v>8.15</v>
       </c>
       <c r="M135">
         <v>0.84455000000000002</v>
@@ -17301,10 +17301,10 @@
         <v>1365</v>
       </c>
       <c r="H178">
-        <v>56.2</v>
+        <v>60.2</v>
       </c>
       <c r="I178">
-        <v>8.15</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="M178">
         <v>0.84455000000000002</v>
@@ -17363,10 +17363,10 @@
         <v>1365</v>
       </c>
       <c r="H179">
-        <v>60.2</v>
+        <v>56.2</v>
       </c>
       <c r="I179">
-        <v>8.5500000000000007</v>
+        <v>8.15</v>
       </c>
       <c r="M179">
         <v>0.84455000000000002</v>
@@ -17673,10 +17673,10 @@
         <v>1365</v>
       </c>
       <c r="H184">
-        <v>60.2</v>
+        <v>56.2</v>
       </c>
       <c r="I184">
-        <v>8.5499999999999989</v>
+        <v>8.15</v>
       </c>
       <c r="M184">
         <v>0.84455000000000002</v>
@@ -17735,10 +17735,10 @@
         <v>1365</v>
       </c>
       <c r="H185">
-        <v>56.2</v>
+        <v>60.2</v>
       </c>
       <c r="I185">
-        <v>8.15</v>
+        <v>8.5499999999999989</v>
       </c>
       <c r="M185">
         <v>0.84455000000000002</v>
@@ -17859,10 +17859,10 @@
         <v>1365</v>
       </c>
       <c r="H187">
-        <v>56.2</v>
+        <v>60.2</v>
       </c>
       <c r="I187">
-        <v>8.15</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="M187">
         <v>0.84455000000000002</v>
@@ -17921,10 +17921,10 @@
         <v>1365</v>
       </c>
       <c r="H188">
-        <v>60.2</v>
+        <v>56.2</v>
       </c>
       <c r="I188">
-        <v>8.5500000000000007</v>
+        <v>8.15</v>
       </c>
       <c r="M188">
         <v>0.84455000000000002</v>
@@ -18045,10 +18045,10 @@
         <v>1365</v>
       </c>
       <c r="H190">
-        <v>60.2</v>
+        <v>56.2</v>
       </c>
       <c r="I190">
-        <v>8.5500000000000007</v>
+        <v>8.15</v>
       </c>
       <c r="M190">
         <v>0.84455000000000002</v>
@@ -18107,10 +18107,10 @@
         <v>1365</v>
       </c>
       <c r="H191">
-        <v>56.2</v>
+        <v>60.2</v>
       </c>
       <c r="I191">
-        <v>8.15</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="M191">
         <v>0.84455000000000002</v>
@@ -19705,7 +19705,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6696590E-491D-45F1-A2E7-333E7FD00FE2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{028086AB-5F4A-439E-9A10-E000FF1E35D7}">
   <dimension ref="B9:Y462"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26214,7 +26214,7 @@
         <v>30</v>
       </c>
       <c r="P115">
-        <v>0.39244376840277601</v>
+        <v>0.39145283147519688</v>
       </c>
       <c r="R115" t="s">
         <v>603</v>
@@ -27702,7 +27702,7 @@
         <v>30</v>
       </c>
       <c r="P139">
-        <v>0.31194715261764772</v>
+        <v>0.3160452326957392</v>
       </c>
       <c r="R139" t="s">
         <v>603</v>
@@ -27764,7 +27764,7 @@
         <v>30</v>
       </c>
       <c r="P140">
-        <v>0.31194715261764772</v>
+        <v>0.3160452326957392</v>
       </c>
       <c r="R140" t="s">
         <v>603</v>
@@ -31958,7 +31958,7 @@
         <v>282</v>
       </c>
       <c r="E209" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="F209">
         <v>2025</v>
@@ -32182,7 +32182,7 @@
         <v>17</v>
       </c>
       <c r="E213" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F213">
         <v>2025</v>
@@ -32238,7 +32238,7 @@
         <v>17</v>
       </c>
       <c r="E214" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F214">
         <v>2025</v>
@@ -39137,7 +39137,7 @@
         <v>30</v>
       </c>
       <c r="P326">
-        <v>0.1621991534540291</v>
+        <v>0.16351051487216889</v>
       </c>
       <c r="R326" t="s">
         <v>603</v>
@@ -39881,7 +39881,7 @@
         <v>30</v>
       </c>
       <c r="P338">
-        <v>0.1621991534540291</v>
+        <v>0.16351051487216889</v>
       </c>
       <c r="R338" t="s">
         <v>603</v>
@@ -40749,7 +40749,7 @@
         <v>30</v>
       </c>
       <c r="P352">
-        <v>0.39244376840277601</v>
+        <v>0.39145283147519694</v>
       </c>
       <c r="R352" t="s">
         <v>603</v>
@@ -40811,7 +40811,7 @@
         <v>30</v>
       </c>
       <c r="P353">
-        <v>0.39244376840277595</v>
+        <v>0.39145283147519694</v>
       </c>
       <c r="R353" t="s">
         <v>603</v>
@@ -42237,7 +42237,7 @@
         <v>30</v>
       </c>
       <c r="P376">
-        <v>0.39244376840277601</v>
+        <v>0.39145283147519688</v>
       </c>
       <c r="R376" t="s">
         <v>603</v>
@@ -42299,7 +42299,7 @@
         <v>30</v>
       </c>
       <c r="P377">
-        <v>0.39244376840277601</v>
+        <v>0.39145283147519688</v>
       </c>
       <c r="R377" t="s">
         <v>603</v>
@@ -42423,7 +42423,7 @@
         <v>30</v>
       </c>
       <c r="P379">
-        <v>0.30523257576223101</v>
+        <v>0.29930787174999712</v>
       </c>
       <c r="R379" t="s">
         <v>603</v>
@@ -43911,7 +43911,7 @@
         <v>30</v>
       </c>
       <c r="P403">
-        <v>0.39244376840277601</v>
+        <v>0.39145283147519688</v>
       </c>
       <c r="R403" t="s">
         <v>603</v>
@@ -43973,7 +43973,7 @@
         <v>30</v>
       </c>
       <c r="P404">
-        <v>0.39244376840277601</v>
+        <v>0.39145283147519688</v>
       </c>
       <c r="R404" t="s">
         <v>603</v>
@@ -45833,7 +45833,7 @@
         <v>30</v>
       </c>
       <c r="P434">
-        <v>0.31194715261764772</v>
+        <v>0.3160452326957392</v>
       </c>
       <c r="R434" t="s">
         <v>603</v>
@@ -46195,7 +46195,7 @@
         <v>30</v>
       </c>
       <c r="P441">
-        <v>0.30523257576223101</v>
+        <v>0.29930787174999712</v>
       </c>
     </row>
     <row r="442" spans="2:25" x14ac:dyDescent="0.45">
@@ -46309,7 +46309,7 @@
         <v>30</v>
       </c>
       <c r="P444">
-        <v>0.30523257576223101</v>
+        <v>0.29930787174999712</v>
       </c>
     </row>
     <row r="445" spans="2:25" x14ac:dyDescent="0.45">
@@ -47002,7 +47002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C46262DA-A99C-4AEC-9FF6-6DECC0EED4FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B04F37E-9251-40B9-908E-874BA81E03D6}">
   <dimension ref="B9:Y674"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -60119,7 +60119,7 @@
         <v>603</v>
       </c>
       <c r="S233" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="T233" t="s">
         <v>17</v>
@@ -60178,7 +60178,7 @@
         <v>603</v>
       </c>
       <c r="S234" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="T234" t="s">
         <v>17</v>
@@ -60237,7 +60237,7 @@
         <v>603</v>
       </c>
       <c r="S235" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="T235" t="s">
         <v>17</v>
@@ -60299,7 +60299,7 @@
         <v>603</v>
       </c>
       <c r="S236" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="T236" t="s">
         <v>17</v>
@@ -60358,7 +60358,7 @@
         <v>603</v>
       </c>
       <c r="S237" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="T237" t="s">
         <v>17</v>
@@ -60417,7 +60417,7 @@
         <v>603</v>
       </c>
       <c r="S238" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="T238" t="s">
         <v>17</v>
@@ -60986,10 +60986,10 @@
         <v>2022</v>
       </c>
       <c r="G248">
-        <v>1.2360817181770572E-2</v>
+        <v>1.2411105290728142E-2</v>
       </c>
       <c r="H248">
-        <v>0.33123000000000002</v>
+        <v>0.33122999999999997</v>
       </c>
       <c r="O248">
         <v>33</v>
@@ -61036,7 +61036,7 @@
         <v>2024</v>
       </c>
       <c r="G249">
-        <v>1.5089639252662835E-2</v>
+        <v>1.5151029160118746E-2</v>
       </c>
       <c r="H249">
         <v>0.33123000000000002</v>
@@ -61080,16 +61080,16 @@
         <v>282</v>
       </c>
       <c r="E250" t="s">
-        <v>285</v>
+        <v>21</v>
       </c>
       <c r="F250">
         <v>2022</v>
       </c>
       <c r="G250">
-        <v>1.2411105290728142E-2</v>
+        <v>2.9871136720796256E-2</v>
       </c>
       <c r="H250">
-        <v>0.33122999999999997</v>
+        <v>0.33123000000000008</v>
       </c>
       <c r="O250">
         <v>33</v>
@@ -61130,13 +61130,13 @@
         <v>282</v>
       </c>
       <c r="E251" t="s">
-        <v>285</v>
+        <v>21</v>
       </c>
       <c r="F251">
         <v>2024</v>
       </c>
       <c r="G251">
-        <v>1.5151029160118746E-2</v>
+        <v>3.6465605028810917E-2</v>
       </c>
       <c r="H251">
         <v>0.33123000000000002</v>
@@ -61171,7 +61171,7 @@
     </row>
     <row r="252" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B252" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C252" t="s">
         <v>17</v>
@@ -61180,16 +61180,16 @@
         <v>282</v>
       </c>
       <c r="E252" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F252">
         <v>2022</v>
       </c>
       <c r="G252">
-        <v>2.9871136720796256E-2</v>
+        <v>2.1020429544264033E-2</v>
       </c>
       <c r="H252">
-        <v>0.33123000000000008</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="O252">
         <v>33</v>
@@ -61221,7 +61221,7 @@
     </row>
     <row r="253" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B253" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C253" t="s">
         <v>17</v>
@@ -61230,13 +61230,13 @@
         <v>282</v>
       </c>
       <c r="E253" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F253">
         <v>2024</v>
       </c>
       <c r="G253">
-        <v>3.6465605028810917E-2</v>
+        <v>2.5660981316570648E-2</v>
       </c>
       <c r="H253">
         <v>0.33123000000000002</v>
@@ -61271,7 +61271,7 @@
     </row>
     <row r="254" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B254" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C254" t="s">
         <v>17</v>
@@ -61280,13 +61280,13 @@
         <v>282</v>
       </c>
       <c r="E254" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F254">
         <v>2022</v>
       </c>
       <c r="G254">
-        <v>2.1020429544264033E-2</v>
+        <v>2.011524358302778E-2</v>
       </c>
       <c r="H254">
         <v>0.33123000000000002</v>
@@ -61321,7 +61321,7 @@
     </row>
     <row r="255" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B255" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C255" t="s">
         <v>17</v>
@@ -61330,13 +61330,13 @@
         <v>282</v>
       </c>
       <c r="E255" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F255">
         <v>2024</v>
       </c>
       <c r="G255">
-        <v>2.5660981316570648E-2</v>
+        <v>2.4555962982364257E-2</v>
       </c>
       <c r="H255">
         <v>0.33123000000000002</v>
@@ -61371,7 +61371,7 @@
     </row>
     <row r="256" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B256" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C256" t="s">
         <v>17</v>
@@ -61380,13 +61380,13 @@
         <v>282</v>
       </c>
       <c r="E256" t="s">
-        <v>34</v>
+        <v>288</v>
       </c>
       <c r="F256">
         <v>2022</v>
       </c>
       <c r="G256">
-        <v>2.011524358302778E-2</v>
+        <v>1.0902462022001057E-2</v>
       </c>
       <c r="H256">
         <v>0.33123000000000002</v>
@@ -61421,7 +61421,7 @@
     </row>
     <row r="257" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B257" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C257" t="s">
         <v>17</v>
@@ -61430,16 +61430,16 @@
         <v>282</v>
       </c>
       <c r="E257" t="s">
-        <v>34</v>
+        <v>288</v>
       </c>
       <c r="F257">
         <v>2024</v>
       </c>
       <c r="G257">
-        <v>2.4555962982364257E-2</v>
+        <v>1.3309331936441427E-2</v>
       </c>
       <c r="H257">
-        <v>0.33123000000000002</v>
+        <v>0.33122999999999997</v>
       </c>
       <c r="O257">
         <v>31</v>
@@ -61786,7 +61786,7 @@
         <v>2022</v>
       </c>
       <c r="G264">
-        <v>1.5800523834468321E-2</v>
+        <v>1.7258878994237836E-2</v>
       </c>
       <c r="H264">
         <v>0.33123000000000002</v>
@@ -61836,7 +61836,7 @@
         <v>2024</v>
       </c>
       <c r="G265">
-        <v>1.9288708922647124E-2</v>
+        <v>2.1069016238868532E-2</v>
       </c>
       <c r="H265">
         <v>0.33123000000000002</v>
@@ -62198,7 +62198,7 @@
         <v>282</v>
       </c>
       <c r="E272" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="F272">
         <v>1977</v>
@@ -62257,7 +62257,7 @@
         <v>282</v>
       </c>
       <c r="E273" t="s">
-        <v>283</v>
+        <v>160</v>
       </c>
       <c r="F273">
         <v>1992</v>
@@ -62670,7 +62670,7 @@
         <v>282</v>
       </c>
       <c r="E280" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="F280">
         <v>1938</v>
@@ -62847,7 +62847,7 @@
         <v>282</v>
       </c>
       <c r="E283" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="F283">
         <v>1953</v>
@@ -63832,7 +63832,7 @@
         <v>282</v>
       </c>
       <c r="E300" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="F300">
         <v>1960</v>
@@ -64068,7 +64068,7 @@
         <v>282</v>
       </c>
       <c r="E304" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="F304">
         <v>1962</v>
@@ -64245,7 +64245,7 @@
         <v>282</v>
       </c>
       <c r="E307" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="F307">
         <v>1957</v>
@@ -64481,7 +64481,7 @@
         <v>282</v>
       </c>
       <c r="E311" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="F311">
         <v>1967</v>
@@ -64658,7 +64658,7 @@
         <v>282</v>
       </c>
       <c r="E314" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F314">
         <v>1924</v>
@@ -65355,7 +65355,7 @@
         <v>17</v>
       </c>
       <c r="U325" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="V325" t="s">
         <v>599</v>
@@ -65396,7 +65396,7 @@
         <v>33</v>
       </c>
       <c r="P326">
-        <v>0.19099682406078569</v>
+        <v>0.19100668392107248</v>
       </c>
       <c r="R326" t="s">
         <v>603</v>
@@ -65408,7 +65408,7 @@
         <v>17</v>
       </c>
       <c r="U326" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="V326" t="s">
         <v>599</v>
@@ -65449,7 +65449,7 @@
         <v>32</v>
       </c>
       <c r="P327">
-        <v>0.19099682406078569</v>
+        <v>0.19100668392107248</v>
       </c>
       <c r="R327" t="s">
         <v>603</v>
@@ -65502,7 +65502,7 @@
         <v>31</v>
       </c>
       <c r="P328">
-        <v>0.19099682406078569</v>
+        <v>0.19100668392107248</v>
       </c>
       <c r="R328" t="s">
         <v>603</v>
@@ -65555,7 +65555,7 @@
         <v>33</v>
       </c>
       <c r="P329">
-        <v>0.19099682406078569</v>
+        <v>0.19100668392107248</v>
       </c>
       <c r="R329" t="s">
         <v>603</v>
@@ -65608,7 +65608,7 @@
         <v>32</v>
       </c>
       <c r="P330">
-        <v>0.19099682406078569</v>
+        <v>0.19100668392107248</v>
       </c>
       <c r="R330" t="s">
         <v>603</v>
@@ -65661,7 +65661,7 @@
         <v>31</v>
       </c>
       <c r="P331">
-        <v>0.19099682406078569</v>
+        <v>0.19100668392107248</v>
       </c>
       <c r="R331" t="s">
         <v>603</v>
@@ -65714,7 +65714,7 @@
         <v>33</v>
       </c>
       <c r="P332">
-        <v>0.19099682406078569</v>
+        <v>0.19100668392107248</v>
       </c>
       <c r="R332" t="s">
         <v>603</v>
@@ -65767,7 +65767,7 @@
         <v>32</v>
       </c>
       <c r="P333">
-        <v>0.19099682406078569</v>
+        <v>0.19100668392107248</v>
       </c>
       <c r="R333" t="s">
         <v>603</v>
@@ -65820,7 +65820,7 @@
         <v>31</v>
       </c>
       <c r="P334">
-        <v>0.19099682406078569</v>
+        <v>0.19100668392107248</v>
       </c>
       <c r="R334" t="s">
         <v>603</v>
@@ -65832,7 +65832,7 @@
         <v>17</v>
       </c>
       <c r="U334" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="V334" t="s">
         <v>599</v>
@@ -65894,7 +65894,7 @@
         <v>17</v>
       </c>
       <c r="U335" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="V335" t="s">
         <v>599</v>
@@ -66142,7 +66142,7 @@
         <v>17</v>
       </c>
       <c r="U339" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="V339" t="s">
         <v>599</v>
@@ -66204,7 +66204,7 @@
         <v>17</v>
       </c>
       <c r="U340" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="V340" t="s">
         <v>599</v>
@@ -68250,7 +68250,7 @@
         <v>17</v>
       </c>
       <c r="U373" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="V373" t="s">
         <v>599</v>
@@ -68312,7 +68312,7 @@
         <v>17</v>
       </c>
       <c r="U374" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="V374" t="s">
         <v>599</v>
@@ -72826,7 +72826,7 @@
         <v>40</v>
       </c>
       <c r="P447">
-        <v>0.1621991534540291</v>
+        <v>0.16351051487216889</v>
       </c>
       <c r="R447" t="s">
         <v>603</v>
@@ -77329,7 +77329,7 @@
         <v>33</v>
       </c>
       <c r="P555">
-        <v>0.2907928894200893</v>
+        <v>0.29073319498749928</v>
       </c>
     </row>
     <row r="556" spans="2:16" x14ac:dyDescent="0.45">
@@ -77358,7 +77358,7 @@
         <v>32</v>
       </c>
       <c r="P556">
-        <v>0.2907928894200893</v>
+        <v>0.29073319498749928</v>
       </c>
     </row>
     <row r="557" spans="2:16" x14ac:dyDescent="0.45">
@@ -77387,7 +77387,7 @@
         <v>33</v>
       </c>
       <c r="P557">
-        <v>0.2907928894200893</v>
+        <v>0.29073319498749928</v>
       </c>
     </row>
     <row r="558" spans="2:16" x14ac:dyDescent="0.45">
@@ -77416,7 +77416,7 @@
         <v>32</v>
       </c>
       <c r="P558">
-        <v>0.2907928894200893</v>
+        <v>0.29073319498749928</v>
       </c>
     </row>
     <row r="559" spans="2:16" x14ac:dyDescent="0.45">
@@ -77445,7 +77445,7 @@
         <v>33</v>
       </c>
       <c r="P559">
-        <v>0.2907928894200893</v>
+        <v>0.29073319498749928</v>
       </c>
     </row>
     <row r="560" spans="2:16" x14ac:dyDescent="0.45">
@@ -77474,7 +77474,7 @@
         <v>32</v>
       </c>
       <c r="P560">
-        <v>0.2907928894200893</v>
+        <v>0.29073319498749928</v>
       </c>
     </row>
     <row r="561" spans="2:16" x14ac:dyDescent="0.45">
@@ -77702,7 +77702,7 @@
         <v>53</v>
       </c>
       <c r="P566">
-        <v>0.39244376840277601</v>
+        <v>0.39145283147519688</v>
       </c>
     </row>
     <row r="567" spans="2:16" x14ac:dyDescent="0.45">
@@ -77740,7 +77740,7 @@
         <v>51</v>
       </c>
       <c r="P567">
-        <v>0.39244376840277595</v>
+        <v>0.39145283147519688</v>
       </c>
     </row>
     <row r="568" spans="2:16" x14ac:dyDescent="0.45">
@@ -77778,7 +77778,7 @@
         <v>48</v>
       </c>
       <c r="P568">
-        <v>0.39244376840277601</v>
+        <v>0.39145283147519688</v>
       </c>
     </row>
     <row r="569" spans="2:16" x14ac:dyDescent="0.45">
@@ -77816,7 +77816,7 @@
         <v>35</v>
       </c>
       <c r="P569">
-        <v>0.39244376840277601</v>
+        <v>0.39145283147519688</v>
       </c>
     </row>
     <row r="570" spans="2:16" x14ac:dyDescent="0.45">
@@ -79108,7 +79108,7 @@
         <v>42</v>
       </c>
       <c r="P603">
-        <v>0.31194715261764772</v>
+        <v>0.3160452326957392</v>
       </c>
     </row>
     <row r="604" spans="2:16" x14ac:dyDescent="0.45">
@@ -80704,7 +80704,7 @@
         <v>35</v>
       </c>
       <c r="P645">
-        <v>0.30523257576223101</v>
+        <v>0.29930787174999712</v>
       </c>
     </row>
     <row r="646" spans="2:16" x14ac:dyDescent="0.45">
@@ -81815,7 +81815,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB256452-FB60-49FD-BC32-1A608B749040}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CAAD653-6C15-4BD1-8B7F-B3D94F5F439B}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
